--- a/Experiments/outputs/scenario_5_np.xlsx
+++ b/Experiments/outputs/scenario_5_np.xlsx
@@ -530,55 +530,55 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>986.8184697527811</v>
+        <v>771.3357656887807</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1045801639556885</v>
+        <v>0.1093208789825439</v>
       </c>
       <c r="E2" t="n">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="F2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H2" t="n">
-        <v>570.6816294962711</v>
+        <v>696.1828561813094</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2196898460388184</v>
+        <v>0.3493428230285645</v>
       </c>
       <c r="J2" t="n">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="K2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="L2" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="M2" t="n">
-        <v>1220.733099769483</v>
+        <v>1196.023842742606</v>
       </c>
       <c r="N2" t="n">
-        <v>1.548033952713013</v>
+        <v>1.39683198928833</v>
       </c>
       <c r="O2" t="n">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="P2" t="n">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="Q2" t="n">
-        <v>84</v>
+        <v>144</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1916181596623152</v>
+        <v>0.3550832867010173</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5325090885108008</v>
+        <v>0.4179189149065036</v>
       </c>
     </row>
     <row r="3">
@@ -591,55 +591,55 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>837.795711111994</v>
+        <v>684.7382699684214</v>
       </c>
       <c r="D3" t="n">
-        <v>0.06935596466064453</v>
+        <v>0.1054689884185791</v>
       </c>
       <c r="E3" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F3" t="n">
+        <v>8</v>
+      </c>
+      <c r="G3" t="n">
         <v>9</v>
       </c>
-      <c r="G3" t="n">
-        <v>6</v>
-      </c>
       <c r="H3" t="n">
-        <v>770.6532567242525</v>
+        <v>641.1697535410619</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1566300392150879</v>
+        <v>0.4841489791870117</v>
       </c>
       <c r="J3" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="K3" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="L3" t="n">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="M3" t="n">
-        <v>1193.499276086736</v>
+        <v>1171.809683953563</v>
       </c>
       <c r="N3" t="n">
-        <v>1.314071893692017</v>
+        <v>1.32259726524353</v>
       </c>
       <c r="O3" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="P3" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="Q3" t="n">
-        <v>192</v>
+        <v>129</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2980341690202178</v>
+        <v>0.4156574404999059</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3542909726337811</v>
+        <v>0.4528379801591822</v>
       </c>
     </row>
     <row r="4">
@@ -652,55 +652,55 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>921.3875536470968</v>
+        <v>680.74633585418</v>
       </c>
       <c r="D4" t="n">
-        <v>0.05992412567138672</v>
+        <v>0.1444518566131592</v>
       </c>
       <c r="E4" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="F4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H4" t="n">
-        <v>685.2178313162354</v>
+        <v>638.4179961666447</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1627669334411621</v>
+        <v>0.6895730495452881</v>
       </c>
       <c r="J4" t="n">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="K4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L4" t="n">
-        <v>95</v>
+        <v>142</v>
       </c>
       <c r="M4" t="n">
-        <v>1193.677533914859</v>
+        <v>1303.171223643112</v>
       </c>
       <c r="N4" t="n">
-        <v>1.267714977264404</v>
+        <v>1.789818286895752</v>
       </c>
       <c r="O4" t="n">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="P4" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="Q4" t="n">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2281101658793422</v>
+        <v>0.4776232597040451</v>
       </c>
       <c r="S4" t="n">
-        <v>0.425960687164018</v>
+        <v>0.5101042866938854</v>
       </c>
     </row>
     <row r="5">
@@ -713,55 +713,55 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>844.8414828420623</v>
+        <v>881.5617547867885</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05280685424804688</v>
+        <v>0.20035719871521</v>
       </c>
       <c r="E5" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>631.0421526023684</v>
+        <v>733.8601789472639</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1771900653839111</v>
+        <v>0.8897590637207031</v>
       </c>
       <c r="J5" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="K5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L5" t="n">
-        <v>99</v>
+        <v>126</v>
       </c>
       <c r="M5" t="n">
-        <v>1265.852097402377</v>
+        <v>1221.55153311647</v>
       </c>
       <c r="N5" t="n">
-        <v>1.545928001403809</v>
+        <v>1.649711132049561</v>
       </c>
       <c r="O5" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="P5" t="n">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="Q5" t="n">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3325906837175213</v>
+        <v>0.2783261852754477</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5014882434548918</v>
+        <v>0.3992392796765513</v>
       </c>
     </row>
     <row r="6">
@@ -774,55 +774,55 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>941.6318552601908</v>
+        <v>862.0215638714062</v>
       </c>
       <c r="D6" t="n">
-        <v>0.06314802169799805</v>
+        <v>0.1594197750091553</v>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="F6" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H6" t="n">
-        <v>629.6457869226638</v>
+        <v>585.5317290369934</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2254819869995117</v>
+        <v>0.6647439002990723</v>
       </c>
       <c r="J6" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="K6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L6" t="n">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="M6" t="n">
-        <v>1190.152121868723</v>
+        <v>1224.049594640343</v>
       </c>
       <c r="N6" t="n">
-        <v>1.710129022598267</v>
+        <v>1.73839807510376</v>
       </c>
       <c r="O6" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="P6" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="Q6" t="n">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2088138667671463</v>
+        <v>0.2957625510878993</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4709535232067456</v>
+        <v>0.5216437866563426</v>
       </c>
     </row>
     <row r="7">
@@ -835,55 +835,55 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>801.3687581143707</v>
+        <v>803.832788279943</v>
       </c>
       <c r="D7" t="n">
-        <v>0.06429910659790039</v>
+        <v>0.1143333911895752</v>
       </c>
       <c r="E7" t="n">
         <v>74</v>
       </c>
       <c r="F7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G7" t="n">
         <v>4</v>
       </c>
       <c r="H7" t="n">
-        <v>641.8173603431569</v>
+        <v>663.2579449412547</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1640188694000244</v>
+        <v>0.536113977432251</v>
       </c>
       <c r="J7" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="K7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L7" t="n">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="M7" t="n">
-        <v>1183.106695786651</v>
+        <v>1247.667781209502</v>
       </c>
       <c r="N7" t="n">
-        <v>1.25628399848938</v>
+        <v>1.265223026275635</v>
       </c>
       <c r="O7" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="P7" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="Q7" t="n">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3226572371128889</v>
+        <v>0.3557317096858111</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4575152328789662</v>
+        <v>0.4684018014007817</v>
       </c>
     </row>
     <row r="8">
@@ -896,55 +896,55 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>949.216391567909</v>
+        <v>623.797037114534</v>
       </c>
       <c r="D8" t="n">
-        <v>0.05704998970031738</v>
+        <v>0.09990930557250977</v>
       </c>
       <c r="E8" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" t="n">
+        <v>673.794883967113</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.6112918853759766</v>
+      </c>
+      <c r="J8" t="n">
+        <v>96</v>
+      </c>
+      <c r="K8" t="n">
         <v>14</v>
       </c>
-      <c r="G8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H8" t="n">
-        <v>550.27960198916</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.1831936836242676</v>
-      </c>
-      <c r="J8" t="n">
-        <v>105</v>
-      </c>
-      <c r="K8" t="n">
-        <v>8</v>
-      </c>
       <c r="L8" t="n">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="M8" t="n">
-        <v>1189.200598174446</v>
+        <v>1164.555105498189</v>
       </c>
       <c r="N8" t="n">
-        <v>1.394015073776245</v>
+        <v>1.163143873214722</v>
       </c>
       <c r="O8" t="n">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="P8" t="n">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="Q8" t="n">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2018029649286583</v>
+        <v>0.4643473424577209</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5372693195463408</v>
+        <v>0.4214143403039152</v>
       </c>
     </row>
     <row r="9">
@@ -957,55 +957,55 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>725.9384080008555</v>
+        <v>1037.356332589214</v>
       </c>
       <c r="D9" t="n">
-        <v>0.06481409072875977</v>
+        <v>0.1073982715606689</v>
       </c>
       <c r="E9" t="n">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="F9" t="n">
+        <v>14</v>
+      </c>
+      <c r="G9" t="n">
         <v>9</v>
       </c>
-      <c r="G9" t="n">
-        <v>7</v>
-      </c>
       <c r="H9" t="n">
-        <v>620.3463465025477</v>
+        <v>655.6735044952807</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1747281551361084</v>
+        <v>0.4725360870361328</v>
       </c>
       <c r="J9" t="n">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="K9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L9" t="n">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="M9" t="n">
-        <v>1291.997035516224</v>
+        <v>1245.126990287801</v>
       </c>
       <c r="N9" t="n">
-        <v>1.270442962646484</v>
+        <v>1.165682077407837</v>
       </c>
       <c r="O9" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="P9" t="n">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="Q9" t="n">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4381268779685681</v>
+        <v>0.1668670419316525</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5198546672712099</v>
+        <v>0.47340832733557</v>
       </c>
     </row>
     <row r="10">
@@ -1018,55 +1018,55 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>847.9734637517333</v>
+        <v>885.3855279491793</v>
       </c>
       <c r="D10" t="n">
-        <v>0.06859493255615234</v>
+        <v>0.09307694435119629</v>
       </c>
       <c r="E10" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="F10" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>607.5174450203668</v>
+        <v>602.4259324181652</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1947839260101318</v>
+        <v>0.4396250247955322</v>
       </c>
       <c r="J10" t="n">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="K10" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="L10" t="n">
-        <v>96</v>
+        <v>125</v>
       </c>
       <c r="M10" t="n">
-        <v>1189.980557832567</v>
+        <v>1179.0861270892</v>
       </c>
       <c r="N10" t="n">
-        <v>1.508944988250732</v>
+        <v>1.339561939239502</v>
       </c>
       <c r="O10" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="P10" t="n">
         <v>128</v>
       </c>
       <c r="Q10" t="n">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2874056150159006</v>
+        <v>0.249091726543401</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4894727976674673</v>
+        <v>0.4890738525561581</v>
       </c>
     </row>
     <row r="11">
@@ -1079,55 +1079,55 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>768.2657969005314</v>
+        <v>861.0413895081161</v>
       </c>
       <c r="D11" t="n">
-        <v>0.06367206573486328</v>
+        <v>0.1284348964691162</v>
       </c>
       <c r="E11" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F11" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H11" t="n">
-        <v>703.6203354083131</v>
+        <v>677.5219022355677</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1501920223236084</v>
+        <v>0.6156930923461914</v>
       </c>
       <c r="J11" t="n">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="K11" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="L11" t="n">
-        <v>90</v>
+        <v>116</v>
       </c>
       <c r="M11" t="n">
-        <v>1224.000995242072</v>
+        <v>1273.463988647719</v>
       </c>
       <c r="N11" t="n">
-        <v>1.61562180519104</v>
+        <v>1.352967023849487</v>
       </c>
       <c r="O11" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="P11" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q11" t="n">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3723323756378232</v>
+        <v>0.3238588627681188</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4251472522135023</v>
+        <v>0.4679693275386431</v>
       </c>
     </row>
     <row r="12">
@@ -1140,55 +1140,55 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>896.3166650014651</v>
+        <v>933.9054418885305</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0489661693572998</v>
+        <v>0.08943605422973633</v>
       </c>
       <c r="E12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>623.1867197413883</v>
+        <v>673.2268945863489</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1699249744415283</v>
+        <v>0.4315838813781738</v>
       </c>
       <c r="J12" t="n">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="K12" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="L12" t="n">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="M12" t="n">
-        <v>1205.936187693351</v>
+        <v>1194.232981931533</v>
       </c>
       <c r="N12" t="n">
-        <v>1.192112922668457</v>
+        <v>1.211557149887085</v>
       </c>
       <c r="O12" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="P12" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="Q12" t="n">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2567461909274892</v>
+        <v>0.2179872302822797</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4832340831123195</v>
+        <v>0.4362683791419975</v>
       </c>
     </row>
     <row r="13">
@@ -1201,55 +1201,55 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1070.766466329258</v>
+        <v>802.1640342309373</v>
       </c>
       <c r="D13" t="n">
-        <v>0.05062985420227051</v>
+        <v>0.08856892585754395</v>
       </c>
       <c r="E13" t="n">
         <v>63</v>
       </c>
       <c r="F13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H13" t="n">
-        <v>588.860745105936</v>
+        <v>621.1367223115012</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1631009578704834</v>
+        <v>0.3199882507324219</v>
       </c>
       <c r="J13" t="n">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="K13" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L13" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="M13" t="n">
-        <v>1210.289187693186</v>
+        <v>1194.283489777699</v>
       </c>
       <c r="N13" t="n">
-        <v>1.152168035507202</v>
+        <v>1.154941082000732</v>
       </c>
       <c r="O13" t="n">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="P13" t="n">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="Q13" t="n">
-        <v>109</v>
+        <v>156</v>
       </c>
       <c r="R13" t="n">
-        <v>0.1152804823695555</v>
+        <v>0.3283302992154316</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5134545106295578</v>
+        <v>0.47990847430444</v>
       </c>
     </row>
     <row r="14">
@@ -1262,55 +1262,55 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>724.6090822281147</v>
+        <v>704.7413498986815</v>
       </c>
       <c r="D14" t="n">
-        <v>0.04894614219665527</v>
+        <v>0.09890294075012207</v>
       </c>
       <c r="E14" t="n">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="F14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G14" t="n">
         <v>4</v>
       </c>
       <c r="H14" t="n">
-        <v>685.1290522627803</v>
+        <v>625.9130636465353</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1681389808654785</v>
+        <v>0.4149439334869385</v>
       </c>
       <c r="J14" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="K14" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L14" t="n">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="M14" t="n">
-        <v>1215.132297736297</v>
+        <v>1224.420273283126</v>
       </c>
       <c r="N14" t="n">
-        <v>1.174292087554932</v>
+        <v>1.211897134780884</v>
       </c>
       <c r="O14" t="n">
-        <v>99</v>
+        <v>53</v>
       </c>
       <c r="P14" t="n">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="Q14" t="n">
-        <v>200</v>
+        <v>82</v>
       </c>
       <c r="R14" t="n">
-        <v>0.4036788557278835</v>
+        <v>0.424428551800267</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4361691697775412</v>
+        <v>0.4888086408695032</v>
       </c>
     </row>
     <row r="15">
@@ -1323,55 +1323,55 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>996.4126627826849</v>
+        <v>861.5259913116632</v>
       </c>
       <c r="D15" t="n">
-        <v>0.05469894409179688</v>
+        <v>0.09609174728393555</v>
       </c>
       <c r="E15" t="n">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="F15" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>638.9723702703347</v>
+        <v>644.3686508039632</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1801967620849609</v>
+        <v>0.3168020248413086</v>
       </c>
       <c r="J15" t="n">
         <v>85</v>
       </c>
       <c r="K15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L15" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="M15" t="n">
-        <v>1222.756860646359</v>
+        <v>1256.11935570478</v>
       </c>
       <c r="N15" t="n">
-        <v>1.554863929748535</v>
+        <v>1.546336889266968</v>
       </c>
       <c r="O15" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="P15" t="n">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="Q15" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="R15" t="n">
-        <v>0.1851097345256573</v>
+        <v>0.3141368394659593</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4774330115534423</v>
+        <v>0.4870163827366368</v>
       </c>
     </row>
     <row r="16">
@@ -1384,55 +1384,55 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>737.0036304829615</v>
+        <v>816.3116741140313</v>
       </c>
       <c r="D16" t="n">
-        <v>0.07214522361755371</v>
+        <v>0.1139256954193115</v>
       </c>
       <c r="E16" t="n">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="F16" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G16" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>713.0548576688705</v>
+        <v>601.4072740365466</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1764547824859619</v>
+        <v>0.5618240833282471</v>
       </c>
       <c r="J16" t="n">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="K16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L16" t="n">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="M16" t="n">
-        <v>1239.613470171907</v>
+        <v>1215.49928817946</v>
       </c>
       <c r="N16" t="n">
-        <v>1.322051763534546</v>
+        <v>1.405732870101929</v>
       </c>
       <c r="O16" t="n">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="P16" t="n">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="Q16" t="n">
-        <v>135</v>
+        <v>219</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4054569039325173</v>
+        <v>0.3284145189943473</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4247764526389135</v>
+        <v>0.5052179134244357</v>
       </c>
     </row>
     <row r="17">
@@ -1445,55 +1445,55 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>741.4479445947484</v>
+        <v>716.6645404363074</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0664360523223877</v>
+        <v>0.1150479316711426</v>
       </c>
       <c r="E17" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F17" t="n">
         <v>8</v>
       </c>
       <c r="G17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H17" t="n">
-        <v>620.8006296604345</v>
+        <v>597.4502545681022</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1918179988861084</v>
+        <v>0.3982322216033936</v>
       </c>
       <c r="J17" t="n">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="K17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L17" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M17" t="n">
-        <v>1223.326148739311</v>
+        <v>1134.133052375525</v>
       </c>
       <c r="N17" t="n">
-        <v>1.169981002807617</v>
+        <v>1.17765212059021</v>
       </c>
       <c r="O17" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="P17" t="n">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="Q17" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3939082023556502</v>
+        <v>0.3680948289663182</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4925305648863997</v>
+        <v>0.4732097320356735</v>
       </c>
     </row>
     <row r="18">
@@ -1506,55 +1506,55 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>925.3821151395358</v>
+        <v>785.6867248400152</v>
       </c>
       <c r="D18" t="n">
-        <v>0.05623221397399902</v>
+        <v>0.0849757194519043</v>
       </c>
       <c r="E18" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G18" t="n">
         <v>5</v>
       </c>
       <c r="H18" t="n">
-        <v>622.0485812113236</v>
+        <v>614.7521524506309</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1722028255462646</v>
+        <v>0.4550418853759766</v>
       </c>
       <c r="J18" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="K18" t="n">
         <v>12</v>
       </c>
       <c r="L18" t="n">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="M18" t="n">
-        <v>1222.466379812575</v>
+        <v>1189.754882201401</v>
       </c>
       <c r="N18" t="n">
-        <v>1.414996147155762</v>
+        <v>1.161030054092407</v>
       </c>
       <c r="O18" t="n">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="P18" t="n">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="Q18" t="n">
-        <v>195</v>
+        <v>76</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2430203967806359</v>
+        <v>0.3396230294207653</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4911528108391054</v>
+        <v>0.4832951209973971</v>
       </c>
     </row>
     <row r="19">
@@ -1567,55 +1567,55 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>989.1511746502981</v>
+        <v>875.0529628177283</v>
       </c>
       <c r="D19" t="n">
-        <v>0.05686497688293457</v>
+        <v>0.08689403533935547</v>
       </c>
       <c r="E19" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F19" t="n">
         <v>13</v>
       </c>
       <c r="G19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H19" t="n">
-        <v>823.9418298666228</v>
+        <v>721.1834085098027</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1891319751739502</v>
+        <v>0.4378571510314941</v>
       </c>
       <c r="J19" t="n">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="K19" t="n">
         <v>17</v>
       </c>
       <c r="L19" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="M19" t="n">
-        <v>1173.883711714063</v>
+        <v>1199.023856062009</v>
       </c>
       <c r="N19" t="n">
-        <v>1.183709144592285</v>
+        <v>1.3351149559021</v>
       </c>
       <c r="O19" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="P19" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="Q19" t="n">
-        <v>71</v>
+        <v>120</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1573686858590318</v>
+        <v>0.2701955358155329</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2981060886656885</v>
+        <v>0.3985245540664992</v>
       </c>
     </row>
     <row r="20">
@@ -1628,55 +1628,55 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1043.225769105662</v>
+        <v>774.4692263608149</v>
       </c>
       <c r="D20" t="n">
-        <v>0.05972003936767578</v>
+        <v>0.117891788482666</v>
       </c>
       <c r="E20" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F20" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H20" t="n">
-        <v>616.2523974471679</v>
+        <v>657.6413156224611</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1475210189819336</v>
+        <v>0.5884029865264893</v>
       </c>
       <c r="J20" t="n">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K20" t="n">
         <v>14</v>
       </c>
       <c r="L20" t="n">
-        <v>92</v>
+        <v>119</v>
       </c>
       <c r="M20" t="n">
-        <v>1246.382129108447</v>
+        <v>1184.308460041465</v>
       </c>
       <c r="N20" t="n">
-        <v>1.517296075820923</v>
+        <v>1.271621227264404</v>
       </c>
       <c r="O20" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="P20" t="n">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="Q20" t="n">
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1629968492472733</v>
+        <v>0.3460578451548851</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5055670463696548</v>
+        <v>0.4447043673069463</v>
       </c>
     </row>
     <row r="21">
@@ -1689,55 +1689,55 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>825.1543588213133</v>
+        <v>726.1747732923681</v>
       </c>
       <c r="D21" t="n">
-        <v>0.06432223320007324</v>
+        <v>0.1139991283416748</v>
       </c>
       <c r="E21" t="n">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="F21" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G21" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H21" t="n">
-        <v>636.9776539338617</v>
+        <v>722.776530425314</v>
       </c>
       <c r="I21" t="n">
-        <v>0.25177001953125</v>
+        <v>0.6302540302276611</v>
       </c>
       <c r="J21" t="n">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="K21" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="L21" t="n">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="M21" t="n">
-        <v>1241.703761922291</v>
+        <v>1185.093127571951</v>
       </c>
       <c r="N21" t="n">
-        <v>1.518738269805908</v>
+        <v>1.138901948928833</v>
       </c>
       <c r="O21" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="P21" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Q21" t="n">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3354660071707558</v>
+        <v>0.3872424399421052</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4870131882762828</v>
+        <v>0.3901099300894967</v>
       </c>
     </row>
     <row r="22">
@@ -1750,55 +1750,55 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1034.522557868415</v>
+        <v>890.9796716711057</v>
       </c>
       <c r="D22" t="n">
-        <v>0.07507872581481934</v>
+        <v>0.09594225883483887</v>
       </c>
       <c r="E22" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F22" t="n">
+        <v>13</v>
+      </c>
+      <c r="G22" t="n">
+        <v>4</v>
+      </c>
+      <c r="H22" t="n">
+        <v>663.6861263282583</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.3511688709259033</v>
+      </c>
+      <c r="J22" t="n">
+        <v>78</v>
+      </c>
+      <c r="K22" t="n">
         <v>16</v>
       </c>
-      <c r="G22" t="n">
-        <v>5</v>
-      </c>
-      <c r="H22" t="n">
-        <v>566.6175556536248</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.2825582027435303</v>
-      </c>
-      <c r="J22" t="n">
-        <v>111</v>
-      </c>
-      <c r="K22" t="n">
-        <v>10</v>
-      </c>
       <c r="L22" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="M22" t="n">
-        <v>1254.489225112992</v>
+        <v>1269.925548897768</v>
       </c>
       <c r="N22" t="n">
-        <v>1.1650071144104</v>
+        <v>1.300919771194458</v>
       </c>
       <c r="O22" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P22" t="n">
         <v>139</v>
       </c>
       <c r="Q22" t="n">
-        <v>95</v>
+        <v>133</v>
       </c>
       <c r="R22" t="n">
-        <v>0.1753436082520078</v>
+        <v>0.2984000735756268</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5483280810143353</v>
+        <v>0.4773818615553448</v>
       </c>
     </row>
     <row r="23">
@@ -1811,55 +1811,55 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>940.4708143553225</v>
+        <v>1100.728807534523</v>
       </c>
       <c r="D23" t="n">
-        <v>0.05989670753479004</v>
+        <v>0.07882308959960938</v>
       </c>
       <c r="E23" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F23" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G23" t="n">
         <v>3</v>
       </c>
       <c r="H23" t="n">
-        <v>666.3054591365293</v>
+        <v>754.1427517396938</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2422337532043457</v>
+        <v>0.3690552711486816</v>
       </c>
       <c r="J23" t="n">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="K23" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="L23" t="n">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="M23" t="n">
-        <v>1168.000476882864</v>
+        <v>1231.418314626528</v>
       </c>
       <c r="N23" t="n">
-        <v>1.273346900939941</v>
+        <v>1.175529003143311</v>
       </c>
       <c r="O23" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="P23" t="n">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="Q23" t="n">
-        <v>196</v>
+        <v>157</v>
       </c>
       <c r="R23" t="n">
-        <v>0.1948027137238574</v>
+        <v>0.1061292539989887</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4295332302305631</v>
+        <v>0.3875819916090701</v>
       </c>
     </row>
     <row r="24">
@@ -1872,55 +1872,55 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>824.1995862204427</v>
+        <v>863.0537800652173</v>
       </c>
       <c r="D24" t="n">
-        <v>0.05675721168518066</v>
+        <v>0.09169316291809082</v>
       </c>
       <c r="E24" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F24" t="n">
         <v>12</v>
       </c>
       <c r="G24" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H24" t="n">
-        <v>518.3005389103685</v>
+        <v>688.4693249358415</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2018661499023438</v>
+        <v>0.6409242153167725</v>
       </c>
       <c r="J24" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="K24" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L24" t="n">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="M24" t="n">
-        <v>1226.923473771626</v>
+        <v>1277.397896331181</v>
       </c>
       <c r="N24" t="n">
-        <v>1.230624914169312</v>
+        <v>1.416711091995239</v>
       </c>
       <c r="O24" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="P24" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="Q24" t="n">
-        <v>76</v>
+        <v>142</v>
       </c>
       <c r="R24" t="n">
-        <v>0.3282387990452163</v>
+        <v>0.3243657418381563</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5775608259274022</v>
+        <v>0.4610376869155675</v>
       </c>
     </row>
     <row r="25">
@@ -1933,55 +1933,55 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>786.345432313562</v>
+        <v>952.7778715107042</v>
       </c>
       <c r="D25" t="n">
-        <v>0.05715203285217285</v>
+        <v>0.1033990383148193</v>
       </c>
       <c r="E25" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G25" t="n">
         <v>7</v>
       </c>
       <c r="H25" t="n">
-        <v>718.9518189385107</v>
+        <v>595.811279320896</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1723320484161377</v>
+        <v>0.5169200897216797</v>
       </c>
       <c r="J25" t="n">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="K25" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="L25" t="n">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="M25" t="n">
-        <v>1208.339534603226</v>
+        <v>1204.45397223075</v>
       </c>
       <c r="N25" t="n">
-        <v>1.925240039825439</v>
+        <v>1.330556869506836</v>
       </c>
       <c r="O25" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="P25" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="Q25" t="n">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="R25" t="n">
-        <v>0.349234706144272</v>
+        <v>0.208954519244866</v>
       </c>
       <c r="S25" t="n">
-        <v>0.4050084447707922</v>
+        <v>0.50532665169645</v>
       </c>
     </row>
     <row r="26">
@@ -1994,55 +1994,55 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>837.3478914244432</v>
+        <v>877.0778309385756</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0919952392578125</v>
+        <v>0.1240217685699463</v>
       </c>
       <c r="E26" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="F26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G26" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H26" t="n">
-        <v>696.6545438735075</v>
+        <v>635.7402018950797</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3175480365753174</v>
+        <v>0.6626577377319336</v>
       </c>
       <c r="J26" t="n">
         <v>89</v>
       </c>
       <c r="K26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L26" t="n">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="M26" t="n">
-        <v>1221.377727305269</v>
+        <v>1231.16231176247</v>
       </c>
       <c r="N26" t="n">
-        <v>1.219830751419067</v>
+        <v>1.285141706466675</v>
       </c>
       <c r="O26" t="n">
         <v>60</v>
       </c>
       <c r="P26" t="n">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="Q26" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="R26" t="n">
-        <v>0.3144234803823651</v>
+        <v>0.2876017868976229</v>
       </c>
       <c r="S26" t="n">
-        <v>0.4296158114733766</v>
+        <v>0.4836260046126771</v>
       </c>
     </row>
     <row r="27">
@@ -2055,55 +2055,55 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>981.4187787517184</v>
+        <v>709.9668873222565</v>
       </c>
       <c r="D27" t="n">
-        <v>0.05155825614929199</v>
+        <v>0.1074340343475342</v>
       </c>
       <c r="E27" t="n">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="F27" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="G27" t="n">
         <v>7</v>
       </c>
       <c r="H27" t="n">
-        <v>615.3783295165128</v>
+        <v>576.4530120247283</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2841098308563232</v>
+        <v>0.3748540878295898</v>
       </c>
       <c r="J27" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="K27" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L27" t="n">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="M27" t="n">
-        <v>1187.867082547971</v>
+        <v>1215.269630627294</v>
       </c>
       <c r="N27" t="n">
-        <v>1.236273050308228</v>
+        <v>1.175173997879028</v>
       </c>
       <c r="O27" t="n">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="P27" t="n">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="Q27" t="n">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="R27" t="n">
-        <v>0.1737974785473652</v>
+        <v>0.4157947590973797</v>
       </c>
       <c r="S27" t="n">
-        <v>0.481946811593997</v>
+        <v>0.5256583415754603</v>
       </c>
     </row>
     <row r="28">
@@ -2116,55 +2116,55 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>822.2082656433183</v>
+        <v>723.3367974510417</v>
       </c>
       <c r="D28" t="n">
-        <v>0.05269098281860352</v>
+        <v>0.100226879119873</v>
       </c>
       <c r="E28" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="F28" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G28" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H28" t="n">
-        <v>576.3731339025741</v>
+        <v>695.3749590571886</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1746690273284912</v>
+        <v>0.4950363636016846</v>
       </c>
       <c r="J28" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="K28" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L28" t="n">
-        <v>102</v>
+        <v>123</v>
       </c>
       <c r="M28" t="n">
-        <v>1227.826218157231</v>
+        <v>1270.283312445772</v>
       </c>
       <c r="N28" t="n">
-        <v>1.211238145828247</v>
+        <v>1.46979832649231</v>
       </c>
       <c r="O28" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="P28" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="Q28" t="n">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="R28" t="n">
-        <v>0.3303545294241068</v>
+        <v>0.4305704952871127</v>
       </c>
       <c r="S28" t="n">
-        <v>0.5305743391213643</v>
+        <v>0.452582780357611</v>
       </c>
     </row>
     <row r="29">
@@ -2177,55 +2177,55 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>683.7044942494092</v>
+        <v>913.689810393927</v>
       </c>
       <c r="D29" t="n">
-        <v>0.05750298500061035</v>
+        <v>0.1255769729614258</v>
       </c>
       <c r="E29" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F29" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G29" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H29" t="n">
-        <v>514.7747697712106</v>
+        <v>692.3046635206956</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1535110473632812</v>
+        <v>0.3865160942077637</v>
       </c>
       <c r="J29" t="n">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="K29" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L29" t="n">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="M29" t="n">
-        <v>1293.540394870567</v>
+        <v>1230.904631776993</v>
       </c>
       <c r="N29" t="n">
-        <v>1.295701026916504</v>
+        <v>1.419035196304321</v>
       </c>
       <c r="O29" t="n">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="P29" t="n">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="Q29" t="n">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="R29" t="n">
-        <v>0.4714471253000017</v>
+        <v>0.2577086909853608</v>
       </c>
       <c r="S29" t="n">
-        <v>0.6020419835263672</v>
+        <v>0.4375643363034136</v>
       </c>
     </row>
     <row r="30">
@@ -2238,55 +2238,55 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>949.0070182933935</v>
+        <v>1032.149846000828</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1184172630310059</v>
+        <v>0.1041836738586426</v>
       </c>
       <c r="E30" t="n">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="F30" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G30" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H30" t="n">
-        <v>743.1751380384912</v>
+        <v>728.1955668660917</v>
       </c>
       <c r="I30" t="n">
-        <v>0.261897087097168</v>
+        <v>0.4569029808044434</v>
       </c>
       <c r="J30" t="n">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="K30" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="L30" t="n">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="M30" t="n">
-        <v>1234.551941730505</v>
+        <v>1228.205405271121</v>
       </c>
       <c r="N30" t="n">
-        <v>1.616518259048462</v>
+        <v>1.230771064758301</v>
       </c>
       <c r="O30" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="P30" t="n">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="Q30" t="n">
-        <v>117</v>
+        <v>175</v>
       </c>
       <c r="R30" t="n">
-        <v>0.2312943779723479</v>
+        <v>0.1596276636048632</v>
       </c>
       <c r="S30" t="n">
-        <v>0.3980203562786006</v>
+        <v>0.4071060396405389</v>
       </c>
     </row>
     <row r="31">
@@ -2299,55 +2299,55 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>879.7262344104939</v>
+        <v>878.4107357862596</v>
       </c>
       <c r="D31" t="n">
-        <v>0.06980991363525391</v>
+        <v>0.0976870059967041</v>
       </c>
       <c r="E31" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H31" t="n">
-        <v>644.1414167312787</v>
+        <v>658.4310908523279</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1835970878601074</v>
+        <v>0.3757760524749756</v>
       </c>
       <c r="J31" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K31" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="L31" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="M31" t="n">
-        <v>1196.139612916595</v>
+        <v>1232.428714633551</v>
       </c>
       <c r="N31" t="n">
-        <v>1.52934718132019</v>
+        <v>1.160095930099487</v>
       </c>
       <c r="O31" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="P31" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="Q31" t="n">
-        <v>74</v>
+        <v>111</v>
       </c>
       <c r="R31" t="n">
-        <v>0.2645288017295719</v>
+        <v>0.287252296740388</v>
       </c>
       <c r="S31" t="n">
-        <v>0.4614830829315625</v>
+        <v>0.4657450909458039</v>
       </c>
     </row>
   </sheetData>
